--- a/artfynd/A 39975-2024 artfynd.xlsx
+++ b/artfynd/A 39975-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137123075</v>
       </c>
       <c r="B2" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39975-2024 artfynd.xlsx
+++ b/artfynd/A 39975-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137123075</v>
       </c>
       <c r="B2" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39975-2024 artfynd.xlsx
+++ b/artfynd/A 39975-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137123075</v>
       </c>
       <c r="B2" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39975-2024 artfynd.xlsx
+++ b/artfynd/A 39975-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137123075</v>
       </c>
       <c r="B2" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39975-2024 artfynd.xlsx
+++ b/artfynd/A 39975-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137123075</v>
       </c>
       <c r="B2" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39975-2024 artfynd.xlsx
+++ b/artfynd/A 39975-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137123075</v>
       </c>
       <c r="B2" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
